--- a/tests/FatEq_BM_x_PA_D2_0001.xlsx
+++ b/tests/FatEq_BM_x_PA_D2_0001.xlsx
@@ -533,10 +533,10 @@
         <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>3.869999999999997</v>
+        <v>5.270000000000003</v>
       </c>
       <c r="F2" t="n">
-        <v>38.87</v>
+        <v>40.27</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -660,28 +660,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sem veículos válidos</t>
+          <t>Headway entre veículos foi elevado</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>47.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[8,3]</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -709,11 +709,11 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[18,19,10,13]</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -868,10 +868,10 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>26.19999999999999</v>
+        <v>26.43000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>221.2</v>
+        <v>221.43</v>
       </c>
       <c r="G7" t="n">
         <v>204</v>
@@ -910,11 +910,11 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[129,130,157,205]</t>
+          <t>[128,129,130,157,205]</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -935,10 +935,10 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>17.56999999999999</v>
+        <v>17.83000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>212.57</v>
+        <v>212.83</v>
       </c>
       <c r="G8" t="n">
         <v>166</v>
@@ -977,11 +977,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[131,129,132,157,169]</t>
+          <t>[135,131,128,129,132,157,169]</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1002,10 +1002,10 @@
         <v>355</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8000000000000114</v>
+        <v>2.430000000000007</v>
       </c>
       <c r="F9" t="n">
-        <v>355.8</v>
+        <v>357.43</v>
       </c>
       <c r="G9" t="n">
         <v>253</v>
@@ -1136,10 +1136,10 @@
         <v>355</v>
       </c>
       <c r="E11" t="n">
-        <v>13.37</v>
+        <v>13.67000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>368.37</v>
+        <v>368.67</v>
       </c>
       <c r="G11" t="n">
         <v>265</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[264,282,288,301,310,312]</t>
+          <t>[263,261,264,282,288,301,310,312]</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1203,10 +1203,10 @@
         <v>355</v>
       </c>
       <c r="E12" t="n">
-        <v>7.129999999999995</v>
+        <v>7.5</v>
       </c>
       <c r="F12" t="n">
-        <v>362.13</v>
+        <v>362.5</v>
       </c>
       <c r="G12" t="n">
         <v>266</v>
@@ -1245,11 +1245,11 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[268,264,207,273,287,282]</t>
+          <t>[263,250,251,268,264,207,273,287,282,288]</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1263,20 +1263,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Headway entre veículos foi elevado</t>
+          <t>Sem veículos válidos</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>495</v>
       </c>
       <c r="E13" t="n">
-        <v>2.329999999999984</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>497.33</v>
+        <v>495</v>
       </c>
       <c r="G13" t="n">
-        <v>383</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1288,11 +1288,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[383]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fim do ciclo</t>
+          <t>Sem veículos válidos</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>495</v>
       </c>
       <c r="E14" t="n">
-        <v>4.699999999999989</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>499.7</v>
+        <v>495</v>
       </c>
       <c r="G14" t="n">
-        <v>377</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1355,11 +1355,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[377]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         <v>495</v>
       </c>
       <c r="E15" t="n">
-        <v>28.39999999999998</v>
+        <v>28.63</v>
       </c>
       <c r="F15" t="n">
-        <v>523.4</v>
+        <v>523.63</v>
       </c>
       <c r="G15" t="n">
         <v>468</v>
@@ -1446,11 +1446,11 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[376,380,398,402]</t>
+          <t>[375,376,380,398,402]</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1471,10 +1471,10 @@
         <v>495</v>
       </c>
       <c r="E16" t="n">
-        <v>8.100000000000023</v>
+        <v>8.569999999999993</v>
       </c>
       <c r="F16" t="n">
-        <v>503.1</v>
+        <v>503.57</v>
       </c>
       <c r="G16" t="n">
         <v>406</v>
@@ -1513,11 +1513,11 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[384,390,385,398,396]</t>
+          <t>[384,390,385,396,398,402]</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/tests/FatEq_BM_x_PA_D2_0001.xlsx
+++ b/tests/FatEq_BM_x_PA_D2_0001.xlsx
@@ -709,11 +709,11 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[18,19,10,13]</t>
+          <t>[18,19,10,13,31,14]</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -910,11 +910,11 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[128,129,130,157,205]</t>
+          <t>[128,129,130,132,157,169,205]</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -977,11 +977,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[135,131,128,129,132,157,169]</t>
+          <t>[135,131,132,169]</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1136,21 +1136,21 @@
         <v>355</v>
       </c>
       <c r="E11" t="n">
-        <v>13.67000000000002</v>
+        <v>31.89999999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>368.67</v>
+        <v>386.9</v>
       </c>
       <c r="G11" t="n">
-        <v>265</v>
+        <v>347</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[247,259,262,265]</t>
+          <t>[247,259,262,265,269,281,332,336,341,344,347]</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1245,11 +1245,11 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[263,250,251,268,264,207,273,287,282,288]</t>
+          <t>[250,251,268,207,273,287,282]</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[375,376,380,398,402]</t>
+          <t>[375,376,385,380,398,402]</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1513,11 +1513,11 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[384,390,385,396,398,402]</t>
+          <t>[384,390,385,396,398]</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
